--- a/VALIDA (1).xlsx
+++ b/VALIDA (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87F3F3D-2748-4C97-B548-784035DA72DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C731628C-CC37-4608-AABC-4633761C23D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,18 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -437,7 +436,7 @@
       <c r="A6" s="7">
         <v>46101</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>1340</v>
       </c>
     </row>
@@ -445,21 +444,25 @@
       <c r="A7" s="7">
         <v>46108</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>717</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="7">
+        <v>46119</v>
+      </c>
+      <c r="B8">
+        <v>235</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A9" s="7">
+        <v>46127</v>
+      </c>
+      <c r="B9">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
